--- a/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2022_T4_0.xlsx
+++ b/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2022_T4_0.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="168" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="168" uniqueCount="71">
   <si>
     <t/>
   </si>
@@ -57,7 +57,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>57</t>
+    <t>51</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -69,40 +69,37 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>1.650</t>
-  </si>
-  <si>
-    <t>(0.459)</t>
-  </si>
-  <si>
-    <t>6.895</t>
-  </si>
-  <si>
-    <t>(0.946)</t>
-  </si>
-  <si>
-    <t>12.879</t>
-  </si>
-  <si>
-    <t>(9.748)</t>
-  </si>
-  <si>
-    <t>17.701</t>
-  </si>
-  <si>
-    <t>(9.805)</t>
-  </si>
-  <si>
-    <t>2.424</t>
-  </si>
-  <si>
-    <t>(0.621)</t>
-  </si>
-  <si>
-    <t>10.439</t>
-  </si>
-  <si>
-    <t>(1.308)</t>
+    <t>1.621</t>
+  </si>
+  <si>
+    <t>(0.470)</t>
+  </si>
+  <si>
+    <t>7.686</t>
+  </si>
+  <si>
+    <t>(1.001)</t>
+  </si>
+  <si>
+    <t>2.381</t>
+  </si>
+  <si>
+    <t>6.756</t>
+  </si>
+  <si>
+    <t>(1.120)</t>
+  </si>
+  <si>
+    <t>2.017</t>
+  </si>
+  <si>
+    <t>(0.269)</t>
+  </si>
+  <si>
+    <t>11.569</t>
+  </si>
+  <si>
+    <t>(1.377)</t>
   </si>
   <si>
     <t>0.000</t>
@@ -111,22 +108,22 @@
     <t>(0.000)</t>
   </si>
   <si>
-    <t>0.748</t>
-  </si>
-  <si>
-    <t>(0.219)</t>
-  </si>
-  <si>
-    <t>56.050</t>
-  </si>
-  <si>
-    <t>(43.736)</t>
-  </si>
-  <si>
-    <t>2.913</t>
-  </si>
-  <si>
-    <t>(0.609)</t>
+    <t>0.737</t>
+  </si>
+  <si>
+    <t>(0.227)</t>
+  </si>
+  <si>
+    <t>10.464</t>
+  </si>
+  <si>
+    <t>(1.596)</t>
+  </si>
+  <si>
+    <t>3.217</t>
+  </si>
+  <si>
+    <t>(0.667)</t>
   </si>
   <si>
     <t>59</t>
@@ -165,9 +162,6 @@
     <t>1.821</t>
   </si>
   <si>
-    <t>(0.227)</t>
-  </si>
-  <si>
     <t>11.000</t>
   </si>
   <si>
@@ -192,7 +186,7 @@
     <t>(1.042)</t>
   </si>
   <si>
-    <t>116</t>
+    <t>110</t>
   </si>
   <si>
     <t>.n</t>
@@ -207,31 +201,31 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>-0.059</t>
-  </si>
-  <si>
-    <t>3.563**</t>
-  </si>
-  <si>
-    <t>-7.814</t>
-  </si>
-  <si>
-    <t>-8.816</t>
-  </si>
-  <si>
-    <t>-0.603</t>
-  </si>
-  <si>
-    <t>0.561</t>
-  </si>
-  <si>
-    <t>-0.340</t>
-  </si>
-  <si>
-    <t>-43.154</t>
-  </si>
-  <si>
-    <t>2.466**</t>
+    <t>-0.030</t>
+  </si>
+  <si>
+    <t>2.771*</t>
+  </si>
+  <si>
+    <t>2.683***</t>
+  </si>
+  <si>
+    <t>2.129</t>
+  </si>
+  <si>
+    <t>-0.197</t>
+  </si>
+  <si>
+    <t>-0.569</t>
+  </si>
+  <si>
+    <t>-0.329</t>
+  </si>
+  <si>
+    <t>2.433</t>
+  </si>
+  <si>
+    <t>2.163*</t>
   </si>
 </sst>
 </file>
@@ -292,13 +286,13 @@
         <v>0</v>
       </c>
       <c r="E1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F1" t="s">
         <v>0</v>
       </c>
       <c r="G1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2">
@@ -315,13 +309,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F2" t="s">
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
@@ -344,7 +338,7 @@
         <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4">
@@ -358,16 +352,16 @@
         <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5">
@@ -384,7 +378,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F5" t="s">
         <v>0</v>
@@ -404,16 +398,16 @@
         <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7">
@@ -430,7 +424,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F7" t="s">
         <v>0</v>
@@ -450,16 +444,16 @@
         <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9">
@@ -470,13 +464,13 @@
         <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s">
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F9" t="s">
         <v>0</v>
@@ -493,19 +487,19 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11">
@@ -516,13 +510,13 @@
         <v>0</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F11" t="s">
         <v>0</v>
@@ -539,19 +533,19 @@
         <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -562,13 +556,13 @@
         <v>0</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D13" t="s">
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="F13" t="s">
         <v>0</v>
@@ -585,19 +579,19 @@
         <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15">
@@ -608,13 +602,13 @@
         <v>0</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D15" t="s">
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F15" t="s">
         <v>0</v>
@@ -631,19 +625,19 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17">
@@ -654,13 +648,13 @@
         <v>0</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" t="s">
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F17" t="s">
         <v>0</v>
@@ -677,19 +671,19 @@
         <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E18" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F18" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G18" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19">
@@ -700,13 +694,13 @@
         <v>0</v>
       </c>
       <c r="C19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D19" t="s">
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F19" t="s">
         <v>0</v>
@@ -723,19 +717,19 @@
         <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E20" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F20" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G20" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21">
@@ -746,13 +740,13 @@
         <v>0</v>
       </c>
       <c r="C21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s">
         <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F21" t="s">
         <v>0</v>
@@ -769,19 +763,19 @@
         <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E22" t="s">
+        <v>55</v>
+      </c>
+      <c r="F22" t="s">
         <v>57</v>
       </c>
-      <c r="F22" t="s">
-        <v>59</v>
-      </c>
       <c r="G22" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23">
@@ -792,13 +786,13 @@
         <v>0</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D23" t="s">
         <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F23" t="s">
         <v>0</v>
